--- a/AZcases_Last60.xlsx
+++ b/AZcases_Last60.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1052,6 +1052,60 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>S-0400-CV-202600258</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>J.G. WENTWORTH ORIGINATIONS, LLC PLAINTIFF vs</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Gila County Superior</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6/22/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>J.G. Wentworth</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>S-0400-CV-202600259</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ASSURED MANAGEMENT CORPORATION ASSURED MANAGEMENT CORPORATIO</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Gila County Superior</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>6/23/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Assured Management Corporation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
